--- a/paper_draft/table/ISP prompt.xlsx
+++ b/paper_draft/table/ISP prompt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ker\Desktop\Document\paper\AgentOccam1\paper_draft\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C58693-7B5E-4A31-90F1-50A4F92DBD34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E64A4E-1E22-4CA4-B7FB-A9A3E7A4C14A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13908" xr2:uid="{6B664B9F-B969-4536-AD2D-315EE1B63791}"/>
   </bookViews>
@@ -33,6 +33,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Instruction prompt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Information prompt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Output format and generation rules</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Feature: &lt;feature name&gt;
 Scenario: &lt;scenario name&gt;
 Scenario Steps:
@@ -50,34 +62,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Each test case must be a JSON object with exactly these keys:
+    <t xml:space="preserve">Each test case must be a JSON object with exactly these keys:
 - "name"
 - "expected"
 - "inputs"
 Rules:
-- Return ONLY a valid JSON array.
-- The top-level JSON array must contain between 1 and {max_cases} test case objects.
-- Every "inputs" object must contain exactly these field keys.
+- Return ONLY a valid JSON array — no prose, no markdown fences.
+- The top-level JSON array must contain between 3 and {max_cases} test case objects.
+- Every "inputs" object must contain exactly these keys: {field_keys}
 - Keep values concrete and ready to type into the form.
-- Use each field's original value as the baseline unless the testcase intentionally changes it.
+- Keep each individual input value concise; use representative boundary strings, not thousands of repeated characters.
+- For ordinary non-unique fields, use each field's original value as the baseline unless the testcase intentionally changes it.
 - Include at least one fully valid baseline case.
-- For uniqueness-sensitive fields, use a fresh replacement value in almost every testcase.
-- Reserve at most one deliberate duplicate-existing testcase.
-- If the scenario is about creating a new record, that duplicate-existing testcase should usually have "expected": "fail".
-- Include obvious cross-field dependency cases, such as password confirmation mismatches.
-- Do NOT add explanations, rationales, or extra keys.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instruction prompt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Information prompt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Output format and generation rules</t>
+- For uniqueness-sensitive fields such as email, phone, mobile number, username, employee ID, or other record-unique identifiers:
+  use a fresh valid replacement value in the baseline and in almost every testcase instead of reusing the original value.
+- Reserve at most one deliberate duplicate-existing testcase for those uniqueness-sensitive fields,
+  where the value stays the same as the original input to test whether the system rejects duplicates.
+- If the scenario is clearly about creating or adding a new record, that duplicate-existing testcase should usually have "expected": "fail".
+- Include obvious cross-field dependency cases when labels imply them, such as password confirmation mismatches.
+- Prefer changing one logical validation condition per testcase unless the case is intentionally testing a cross-field dependency.
+- Do NOT add explanations, rationales, or extra keys.
+- All JSON string values must be properly escaped.
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -548,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA9056C-8570-49BA-97AB-FA0F3233C2F9}">
-  <dimension ref="A2:O4"/>
+  <dimension ref="A2:O5"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -557,10 +563,10 @@
     <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" s="2" customFormat="1" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="67.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
@@ -578,13 +584,13 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
     </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" ht="211.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="201.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -599,13 +605,13 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:15" s="4" customFormat="1" ht="277.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" s="4" customFormat="1" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -620,6 +626,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
+    <row r="5" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
